--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N85_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.37291312179724</v>
+        <v>5.260598382292051</v>
       </c>
       <c r="D2" t="n">
-        <v>33.30139704393144</v>
+        <v>5.41147701963886</v>
       </c>
       <c r="E2" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F2" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.35655495770978</v>
+        <v>2.82044018062784</v>
       </c>
       <c r="D3" t="n">
-        <v>14.68370222767784</v>
+        <v>2.386101611997649</v>
       </c>
       <c r="E3" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F3" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.66927070618917</v>
+        <v>4.333756489755741</v>
       </c>
       <c r="D4" t="n">
-        <v>21.73195292139613</v>
+        <v>3.531442349726872</v>
       </c>
       <c r="E4" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F4" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.743547910889625</v>
+        <v>1.420826535519564</v>
       </c>
       <c r="D5" t="n">
-        <v>13.54333239244479</v>
+        <v>2.200791513772279</v>
       </c>
       <c r="E5" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F5" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.071067811865476</v>
+        <v>1.14904851942814</v>
       </c>
       <c r="D6" t="n">
-        <v>7.917982346813131</v>
+        <v>1.286672131357134</v>
       </c>
       <c r="E6" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F6" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.73977856002723</v>
+        <v>6.457714016004426</v>
       </c>
       <c r="D7" t="n">
-        <v>28.69030638657517</v>
+        <v>4.662174787818465</v>
       </c>
       <c r="E7" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F7" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.18774401018181</v>
+        <v>6.368008401654544</v>
       </c>
       <c r="D8" t="n">
-        <v>35.43667926986328</v>
+        <v>5.758460381352783</v>
       </c>
       <c r="E8" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F8" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.830424792767</v>
+        <v>7.447444028824639</v>
       </c>
       <c r="D9" t="n">
-        <v>39.7917539266059</v>
+        <v>6.466160013073459</v>
       </c>
       <c r="E9" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F9" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.56014564772535</v>
+        <v>5.778523667755369</v>
       </c>
       <c r="D10" t="n">
-        <v>35.56689113392655</v>
+        <v>5.779619809263064</v>
       </c>
       <c r="E10" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F10" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.50279893817342</v>
+        <v>4.306704827453181</v>
       </c>
       <c r="D11" t="n">
-        <v>6.270605533805531</v>
+        <v>1.018973399243399</v>
       </c>
       <c r="E11" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F11" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.57139645708981</v>
+        <v>2.205351924277095</v>
       </c>
       <c r="D12" t="n">
-        <v>13.79765743302691</v>
+        <v>2.242119332866872</v>
       </c>
       <c r="E12" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F12" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.86863185996825</v>
+        <v>5.99115267724484</v>
       </c>
       <c r="D13" t="n">
-        <v>37.09105519110754</v>
+        <v>6.027296468554976</v>
       </c>
       <c r="E13" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F13" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.51351831286418</v>
+        <v>3.333446725840429</v>
       </c>
       <c r="D14" t="n">
-        <v>8.52252728415386</v>
+        <v>1.384910683675002</v>
       </c>
       <c r="E14" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F14" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>15.73890437670915</v>
+        <v>2.557571961215237</v>
       </c>
       <c r="D15" t="n">
-        <v>15.69775630289077</v>
+        <v>2.550885399219751</v>
       </c>
       <c r="E15" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F15" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>47.4866916408241</v>
+        <v>7.716587391633916</v>
       </c>
       <c r="D16" t="n">
-        <v>35.46381294596654</v>
+        <v>5.762869603719563</v>
       </c>
       <c r="E16" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F16" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.44592133120176</v>
+        <v>4.134962216320286</v>
       </c>
       <c r="D17" t="n">
-        <v>25.34634907064218</v>
+        <v>4.118781723979355</v>
       </c>
       <c r="E17" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F17" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>42.52376090386451</v>
+        <v>6.910111146877983</v>
       </c>
       <c r="D18" t="n">
-        <v>37.18935177874927</v>
+        <v>6.043269664046757</v>
       </c>
       <c r="E18" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F18" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>34.48418696758595</v>
+        <v>5.603680382232717</v>
       </c>
       <c r="D19" t="n">
-        <v>34.5240930832472</v>
+        <v>5.61016512602767</v>
       </c>
       <c r="E19" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F19" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>7.86089023329221</v>
+        <v>1.277394662909984</v>
       </c>
       <c r="D20" t="n">
-        <v>7.827310573766209</v>
+        <v>1.271937968237009</v>
       </c>
       <c r="E20" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F20" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>55.94832684092527</v>
+        <v>9.091603111650356</v>
       </c>
       <c r="D21" t="n">
-        <v>47.71575611073408</v>
+        <v>7.753810367994289</v>
       </c>
       <c r="E21" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F21" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>17.63344577995701</v>
+        <v>2.865434939243014</v>
       </c>
       <c r="D22" t="n">
-        <v>17.65140822374364</v>
+        <v>2.868353836358342</v>
       </c>
       <c r="E22" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F22" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>38.18791685806764</v>
+        <v>6.205536489435993</v>
       </c>
       <c r="D23" t="n">
-        <v>38.13013106367976</v>
+        <v>6.196146297847962</v>
       </c>
       <c r="E23" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F23" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>28.33743351945877</v>
+        <v>4.60483294691205</v>
       </c>
       <c r="D24" t="n">
-        <v>28.36457522581783</v>
+        <v>4.609243474195398</v>
       </c>
       <c r="E24" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F24" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>73.36245133076879</v>
+        <v>11.92139834124993</v>
       </c>
       <c r="D25" t="n">
-        <v>64.43551413161867</v>
+        <v>10.47077104638804</v>
       </c>
       <c r="E25" t="n">
-        <v>15.80554092815712</v>
+        <v>2.568400400825531</v>
       </c>
       <c r="F25" t="n">
-        <v>14.28356340048401</v>
+        <v>2.321079052578652</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
